--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/53.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/53.xlsx
@@ -426,13 +426,13 @@
         <v>-13.31417917210274</v>
       </c>
       <c r="E2">
-        <v>-14.26869659810599</v>
+        <v>-16.90586534624369</v>
       </c>
       <c r="F2">
-        <v>4.223925591265243</v>
+        <v>3.768411326670212</v>
       </c>
       <c r="G2">
-        <v>-15.33203045074581</v>
+        <v>-12.62899342759208</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.96601970147615</v>
       </c>
       <c r="E3">
-        <v>-14.70264073016937</v>
+        <v>-17.2448338417309</v>
       </c>
       <c r="F3">
-        <v>4.33530952898047</v>
+        <v>3.927325329223269</v>
       </c>
       <c r="G3">
-        <v>-14.0559402665231</v>
+        <v>-12.13479514096188</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.53277343058081</v>
       </c>
       <c r="E4">
-        <v>-14.40784163712172</v>
+        <v>-18.27398299517811</v>
       </c>
       <c r="F4">
-        <v>4.388634852168286</v>
+        <v>3.698338071332596</v>
       </c>
       <c r="G4">
-        <v>-14.21136702963814</v>
+        <v>-12.26686618296483</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.05212305046002</v>
       </c>
       <c r="E5">
-        <v>-15.76364501447802</v>
+        <v>-19.24743343154805</v>
       </c>
       <c r="F5">
-        <v>4.683820262686278</v>
+        <v>4.017763168791308</v>
       </c>
       <c r="G5">
-        <v>-13.03345781188112</v>
+        <v>-11.69312764624948</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.5383210305592</v>
       </c>
       <c r="E6">
-        <v>-17.56334777144332</v>
+        <v>-19.42914888664327</v>
       </c>
       <c r="F6">
-        <v>4.72796893178588</v>
+        <v>4.246364407472276</v>
       </c>
       <c r="G6">
-        <v>-13.56404465662226</v>
+        <v>-11.4445521268681</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.99755801592549</v>
       </c>
       <c r="E7">
-        <v>-18.9506117245852</v>
+        <v>-19.83772105072328</v>
       </c>
       <c r="F7">
-        <v>4.730972591988431</v>
+        <v>4.29917448613555</v>
       </c>
       <c r="G7">
-        <v>-12.3198421068354</v>
+        <v>-11.13589554221144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.44334718733178</v>
       </c>
       <c r="E8">
-        <v>-17.99217514715452</v>
+        <v>-20.88059241438773</v>
       </c>
       <c r="F8">
-        <v>4.675544872332311</v>
+        <v>4.570597349336836</v>
       </c>
       <c r="G8">
-        <v>-12.50608218298706</v>
+        <v>-11.26707632030881</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.885611267925777</v>
       </c>
       <c r="E9">
-        <v>-19.03152043440419</v>
+        <v>-21.60274449312626</v>
       </c>
       <c r="F9">
-        <v>5.493865835270665</v>
+        <v>4.529947704146658</v>
       </c>
       <c r="G9">
-        <v>-12.2566790575703</v>
+        <v>-10.12186798392779</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.317107704141693</v>
       </c>
       <c r="E10">
-        <v>-19.38933204967214</v>
+        <v>-22.33138388795418</v>
       </c>
       <c r="F10">
-        <v>6.077069621537628</v>
+        <v>5.02853873042207</v>
       </c>
       <c r="G10">
-        <v>-11.88963578087798</v>
+        <v>-10.50613956417686</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.749330991783157</v>
       </c>
       <c r="E11">
-        <v>-20.49402396390666</v>
+        <v>-22.3794116237145</v>
       </c>
       <c r="F11">
-        <v>5.729508196875428</v>
+        <v>5.091320695880245</v>
       </c>
       <c r="G11">
-        <v>-11.21726331351037</v>
+        <v>-9.935620075542356</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.17955589191766</v>
       </c>
       <c r="E12">
-        <v>-21.10160140182715</v>
+        <v>-23.27361048158406</v>
       </c>
       <c r="F12">
-        <v>5.834303300268788</v>
+        <v>5.299704799728488</v>
       </c>
       <c r="G12">
-        <v>-10.11799886044376</v>
+        <v>-8.971015217740774</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.601430032863322</v>
       </c>
       <c r="E13">
-        <v>-22.87587819906186</v>
+        <v>-24.72000785756885</v>
       </c>
       <c r="F13">
-        <v>6.404755198737057</v>
+        <v>5.871376055013677</v>
       </c>
       <c r="G13">
-        <v>-10.19303688148153</v>
+        <v>-9.15534031273485</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.028291088713809</v>
       </c>
       <c r="E14">
-        <v>-22.11055764181305</v>
+        <v>-25.64813845196226</v>
       </c>
       <c r="F14">
-        <v>6.263773693719803</v>
+        <v>5.948871482280377</v>
       </c>
       <c r="G14">
-        <v>-9.809699947796075</v>
+        <v>-8.379438768606642</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.455302160180623</v>
       </c>
       <c r="E15">
-        <v>-22.9934306923998</v>
+        <v>-26.08472402642823</v>
       </c>
       <c r="F15">
-        <v>6.967773328132602</v>
+        <v>6.239046926746238</v>
       </c>
       <c r="G15">
-        <v>-9.17376042119745</v>
+        <v>-8.448751426756107</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.884343081865254</v>
       </c>
       <c r="E16">
-        <v>-23.34789066612862</v>
+        <v>-27.09566134821607</v>
       </c>
       <c r="F16">
-        <v>6.905208394933961</v>
+        <v>6.430717889875599</v>
       </c>
       <c r="G16">
-        <v>-9.084982051376643</v>
+        <v>-7.564625381720185</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.322708252049817</v>
       </c>
       <c r="E17">
-        <v>-25.72927974161543</v>
+        <v>-27.62577308850586</v>
       </c>
       <c r="F17">
-        <v>7.830966953280605</v>
+        <v>6.964948595289056</v>
       </c>
       <c r="G17">
-        <v>-9.368315718871804</v>
+        <v>-7.148506633576412</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.764635319856247</v>
       </c>
       <c r="E18">
-        <v>-27.51728290227869</v>
+        <v>-28.49729541254186</v>
       </c>
       <c r="F18">
-        <v>6.906402900728798</v>
+        <v>7.2129535120132</v>
       </c>
       <c r="G18">
-        <v>-8.045760807788747</v>
+        <v>-7.302697209127563</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.216266728860475</v>
       </c>
       <c r="E19">
-        <v>-29.82194347514496</v>
+        <v>-29.15630621950903</v>
       </c>
       <c r="F19">
-        <v>8.085451359829447</v>
+        <v>7.34537963849434</v>
       </c>
       <c r="G19">
-        <v>-8.36155386278522</v>
+        <v>-6.668544737201555</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.682517107852519</v>
       </c>
       <c r="E20">
-        <v>-28.19375796286677</v>
+        <v>-30.58802614667187</v>
       </c>
       <c r="F20">
-        <v>7.642125693199207</v>
+        <v>7.720969702597664</v>
       </c>
       <c r="G20">
-        <v>-8.400178523638445</v>
+        <v>-6.66196827157654</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.164310818368948</v>
       </c>
       <c r="E21">
-        <v>-30.39230813959499</v>
+        <v>-30.50209205114984</v>
       </c>
       <c r="F21">
-        <v>8.07984828271691</v>
+        <v>7.560374114216923</v>
       </c>
       <c r="G21">
-        <v>-8.515765324293099</v>
+        <v>-5.891229474877258</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.679659762848986</v>
       </c>
       <c r="E22">
-        <v>-28.04264544541854</v>
+        <v>-31.37815383516388</v>
       </c>
       <c r="F22">
-        <v>8.506013490230755</v>
+        <v>7.738332283360341</v>
       </c>
       <c r="G22">
-        <v>-8.181656590617672</v>
+        <v>-5.598186448247747</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.239790312081507</v>
       </c>
       <c r="E23">
-        <v>-30.84939188855466</v>
+        <v>-31.7450942089238</v>
       </c>
       <c r="F23">
-        <v>8.467216074553237</v>
+        <v>7.487113301113335</v>
       </c>
       <c r="G23">
-        <v>-7.629272639285333</v>
+        <v>-5.270932224496288</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.856251119294007</v>
       </c>
       <c r="E24">
-        <v>-30.24716794003187</v>
+        <v>-31.51817935498047</v>
       </c>
       <c r="F24">
-        <v>8.858409267055693</v>
+        <v>7.644181701092955</v>
       </c>
       <c r="G24">
-        <v>-5.974057957774918</v>
+        <v>-4.760518603210685</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.547584150209</v>
       </c>
       <c r="E25">
-        <v>-29.58007706043225</v>
+        <v>-31.97095207058497</v>
       </c>
       <c r="F25">
-        <v>8.273886719883473</v>
+        <v>7.656411717427887</v>
       </c>
       <c r="G25">
-        <v>-6.202816620337447</v>
+        <v>-5.055942628907292</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.318444621069468</v>
       </c>
       <c r="E26">
-        <v>-30.39113901060705</v>
+        <v>-32.53559983964637</v>
       </c>
       <c r="F26">
-        <v>8.948494222110138</v>
+        <v>7.182055407888778</v>
       </c>
       <c r="G26">
-        <v>-6.319550843239894</v>
+        <v>-4.415513926984246</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.175699018033842</v>
       </c>
       <c r="E27">
-        <v>-30.88663996432138</v>
+        <v>-32.91857160912014</v>
       </c>
       <c r="F27">
-        <v>8.312197055528143</v>
+        <v>7.401627441879232</v>
       </c>
       <c r="G27">
-        <v>-6.903172353604905</v>
+        <v>-4.390252362320634</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.121578420629023</v>
       </c>
       <c r="E28">
-        <v>-29.81297253868333</v>
+        <v>-32.06200084585352</v>
       </c>
       <c r="F28">
-        <v>8.476058068210719</v>
+        <v>7.355220643239598</v>
       </c>
       <c r="G28">
-        <v>-5.904361520170558</v>
+        <v>-3.960064311575352</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.147611690753816</v>
       </c>
       <c r="E29">
-        <v>-30.77286896989469</v>
+        <v>-31.92111353468702</v>
       </c>
       <c r="F29">
-        <v>8.26822565705274</v>
+        <v>7.038151422674448</v>
       </c>
       <c r="G29">
-        <v>-6.510602521672974</v>
+        <v>-4.101172445980434</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.250357285048645</v>
       </c>
       <c r="E30">
-        <v>-30.22031950542251</v>
+        <v>-32.24445141935324</v>
       </c>
       <c r="F30">
-        <v>8.481006735075043</v>
+        <v>7.026453218212113</v>
       </c>
       <c r="G30">
-        <v>-5.875434470101022</v>
+        <v>-4.104417601507188</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.415985981038308</v>
       </c>
       <c r="E31">
-        <v>-31.24810640555518</v>
+        <v>-32.5393771853463</v>
       </c>
       <c r="F31">
-        <v>8.293981256340583</v>
+        <v>6.828821323252208</v>
       </c>
       <c r="G31">
-        <v>-5.794255977784946</v>
+        <v>-4.309849261148119</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.628691026902583</v>
       </c>
       <c r="E32">
-        <v>-29.85797258338785</v>
+        <v>-31.32581714265405</v>
       </c>
       <c r="F32">
-        <v>8.041980295265335</v>
+        <v>6.445772639054077</v>
       </c>
       <c r="G32">
-        <v>-5.71364140630055</v>
+        <v>-4.419119365264574</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.877745558845345</v>
       </c>
       <c r="E33">
-        <v>-29.58976027263608</v>
+        <v>-32.02578691970668</v>
       </c>
       <c r="F33">
-        <v>7.686382050061173</v>
+        <v>6.874853699825776</v>
       </c>
       <c r="G33">
-        <v>-6.202568599601291</v>
+        <v>-4.188802088181151</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.144483925197741</v>
       </c>
       <c r="E34">
-        <v>-27.50950393746729</v>
+        <v>-31.3539530727741</v>
       </c>
       <c r="F34">
-        <v>8.219641908878549</v>
+        <v>6.850575907984529</v>
       </c>
       <c r="G34">
-        <v>-5.076058415981819</v>
+        <v>-4.783122429880544</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.417539846203685</v>
       </c>
       <c r="E35">
-        <v>-29.54850019472957</v>
+        <v>-30.79160202957533</v>
       </c>
       <c r="F35">
-        <v>7.741456885203701</v>
+        <v>6.916928136948768</v>
       </c>
       <c r="G35">
-        <v>-6.228508957858592</v>
+        <v>-5.098654410417905</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.686308642952137</v>
       </c>
       <c r="E36">
-        <v>-26.78729786698153</v>
+        <v>-29.71052527493379</v>
       </c>
       <c r="F36">
-        <v>7.723413386435922</v>
+        <v>7.206155929105827</v>
       </c>
       <c r="G36">
-        <v>-6.276549269079668</v>
+        <v>-5.135014250338339</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.939529469973626</v>
       </c>
       <c r="E37">
-        <v>-28.0227079544537</v>
+        <v>-29.73067457967619</v>
       </c>
       <c r="F37">
-        <v>7.759467249275368</v>
+        <v>7.222140106510246</v>
       </c>
       <c r="G37">
-        <v>-7.779338238382524</v>
+        <v>-5.249683374269217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.176200106823066</v>
       </c>
       <c r="E38">
-        <v>-28.15660541096051</v>
+        <v>-28.74812861050488</v>
       </c>
       <c r="F38">
-        <v>7.621915185305705</v>
+        <v>7.251091547238089</v>
       </c>
       <c r="G38">
-        <v>-6.887293805001755</v>
+        <v>-5.959427345086319</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.394560749562062</v>
       </c>
       <c r="E39">
-        <v>-27.66161945545046</v>
+        <v>-30.00949419215157</v>
       </c>
       <c r="F39">
-        <v>8.103163511636104</v>
+        <v>7.352210356097824</v>
       </c>
       <c r="G39">
-        <v>-6.422643925653776</v>
+        <v>-6.305619910101714</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.596170295372766</v>
       </c>
       <c r="E40">
-        <v>-26.86975157141335</v>
+        <v>-28.03874350337886</v>
       </c>
       <c r="F40">
-        <v>7.763913925493596</v>
+        <v>7.549635159207031</v>
       </c>
       <c r="G40">
-        <v>-7.944766764026122</v>
+        <v>-6.388409231830508</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.79018099372291</v>
       </c>
       <c r="E41">
-        <v>-26.40686370962723</v>
+        <v>-27.96001522950542</v>
       </c>
       <c r="F41">
-        <v>8.016850941734008</v>
+        <v>7.681608997086243</v>
       </c>
       <c r="G41">
-        <v>-7.259465889443318</v>
+        <v>-6.871882579680412</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.978769083735031</v>
       </c>
       <c r="E42">
-        <v>-25.68280115367928</v>
+        <v>-27.89946140838941</v>
       </c>
       <c r="F42">
-        <v>9.038386995927135</v>
+        <v>7.680643120694579</v>
       </c>
       <c r="G42">
-        <v>-6.901898310244442</v>
+        <v>-7.038659554905321</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.168194394482235</v>
       </c>
       <c r="E43">
-        <v>-24.28189390133533</v>
+        <v>-27.46843283067606</v>
       </c>
       <c r="F43">
-        <v>8.554019037957792</v>
+        <v>7.693981492614456</v>
       </c>
       <c r="G43">
-        <v>-7.959463950701794</v>
+        <v>-7.415384777913785</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.365507325328939</v>
       </c>
       <c r="E44">
-        <v>-23.45716165608486</v>
+        <v>-26.13351179986099</v>
       </c>
       <c r="F44">
-        <v>8.293502459981765</v>
+        <v>8.202420150574348</v>
       </c>
       <c r="G44">
-        <v>-7.175102288726083</v>
+        <v>-7.470487153253822</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.566255798290657</v>
       </c>
       <c r="E45">
-        <v>-23.28526854577285</v>
+        <v>-26.02333956304727</v>
       </c>
       <c r="F45">
-        <v>7.937881020490326</v>
+        <v>7.794894866358297</v>
       </c>
       <c r="G45">
-        <v>-7.090373183766093</v>
+        <v>-7.306198217624245</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.774722194314221</v>
       </c>
       <c r="E46">
-        <v>-22.84949700072654</v>
+        <v>-24.90724708372609</v>
       </c>
       <c r="F46">
-        <v>7.993577131184953</v>
+        <v>8.395951626890396</v>
       </c>
       <c r="G46">
-        <v>-7.575339877522114</v>
+        <v>-7.580240245119634</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.991128004174595</v>
       </c>
       <c r="E47">
-        <v>-23.00033332962167</v>
+        <v>-24.39998215893419</v>
       </c>
       <c r="F47">
-        <v>8.408882442048096</v>
+        <v>8.269512939996691</v>
       </c>
       <c r="G47">
-        <v>-8.350814564909676</v>
+        <v>-7.374088019971555</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.210659760227055</v>
       </c>
       <c r="E48">
-        <v>-21.00101062353981</v>
+        <v>-23.78779880965446</v>
       </c>
       <c r="F48">
-        <v>7.791283184482092</v>
+        <v>8.01063155927379</v>
       </c>
       <c r="G48">
-        <v>-9.273562660054234</v>
+        <v>-7.872165873064148</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.437643889056982</v>
       </c>
       <c r="E49">
-        <v>-21.40348587339496</v>
+        <v>-22.88884452481797</v>
       </c>
       <c r="F49">
-        <v>7.855110549602599</v>
+        <v>8.314480036090259</v>
       </c>
       <c r="G49">
-        <v>-7.171222722263688</v>
+        <v>-7.886425760020809</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.667851652767936</v>
       </c>
       <c r="E50">
-        <v>-20.71857148739484</v>
+        <v>-23.05529692829445</v>
       </c>
       <c r="F50">
-        <v>8.046567793942037</v>
+        <v>8.192173245801717</v>
       </c>
       <c r="G50">
-        <v>-8.915563002625529</v>
+        <v>-8.256769017876298</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.89679917924926</v>
       </c>
       <c r="E51">
-        <v>-19.85618207506214</v>
+        <v>-22.12976209097906</v>
       </c>
       <c r="F51">
-        <v>7.818687234901505</v>
+        <v>8.219453041110711</v>
       </c>
       <c r="G51">
-        <v>-8.426356459653539</v>
+        <v>-8.101701232142533</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.128120668324708</v>
       </c>
       <c r="E52">
-        <v>-20.68172834973229</v>
+        <v>-21.70432373570892</v>
       </c>
       <c r="F52">
-        <v>8.020446056262157</v>
+        <v>8.292597882777908</v>
       </c>
       <c r="G52">
-        <v>-8.455133391909085</v>
+        <v>-8.053782320544943</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.352798021177144</v>
       </c>
       <c r="E53">
-        <v>-19.3884889477732</v>
+        <v>-20.67859682839337</v>
       </c>
       <c r="F53">
-        <v>7.677957553574703</v>
+        <v>8.005939686304332</v>
       </c>
       <c r="G53">
-        <v>-8.746547313913741</v>
+        <v>-8.403676921390538</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.571786415637243</v>
       </c>
       <c r="E54">
-        <v>-18.57184715818349</v>
+        <v>-21.25515393092871</v>
       </c>
       <c r="F54">
-        <v>7.874863798689756</v>
+        <v>8.232332497489438</v>
       </c>
       <c r="G54">
-        <v>-8.623809683824028</v>
+        <v>-8.072240284804115</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.788882568778703</v>
       </c>
       <c r="E55">
-        <v>-18.39362870702377</v>
+        <v>-20.3010616125438</v>
       </c>
       <c r="F55">
-        <v>7.785300715099074</v>
+        <v>8.007399269668065</v>
       </c>
       <c r="G55">
-        <v>-8.202457698147368</v>
+        <v>-8.260963179061921</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.99664058088007</v>
       </c>
       <c r="E56">
-        <v>-18.16616978239689</v>
+        <v>-19.51527402988624</v>
       </c>
       <c r="F56">
-        <v>8.114513801789265</v>
+        <v>7.843493525145739</v>
       </c>
       <c r="G56">
-        <v>-8.889959430420481</v>
+        <v>-8.766928091564267</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.202119972076199</v>
       </c>
       <c r="E57">
-        <v>-16.76362616479096</v>
+        <v>-18.33935869464224</v>
       </c>
       <c r="F57">
-        <v>7.860985331223253</v>
+        <v>7.972821557540409</v>
       </c>
       <c r="G57">
-        <v>-8.127927466932562</v>
+        <v>-8.971263238476929</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.407734988088444</v>
       </c>
       <c r="E58">
-        <v>-16.33048360251327</v>
+        <v>-18.77789627843088</v>
       </c>
       <c r="F58">
-        <v>8.092709515012775</v>
+        <v>8.173518411890672</v>
       </c>
       <c r="G58">
-        <v>-10.20557889849724</v>
+        <v>-9.099641382255744</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.610192271050796</v>
       </c>
       <c r="E59">
-        <v>-17.03341046602918</v>
+        <v>-17.68155647217059</v>
       </c>
       <c r="F59">
-        <v>7.65868807105078</v>
+        <v>8.22816083924894</v>
       </c>
       <c r="G59">
-        <v>-9.787191413303791</v>
+        <v>-9.243360261251938</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.819567430911525</v>
       </c>
       <c r="E60">
-        <v>-17.24856757871192</v>
+        <v>-17.88881002370219</v>
       </c>
       <c r="F60">
-        <v>7.521498832003543</v>
+        <v>7.929136774186374</v>
       </c>
       <c r="G60">
-        <v>-9.496994098278595</v>
+        <v>-9.253475591170208</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.033275081553974</v>
       </c>
       <c r="E61">
-        <v>-17.79053673733409</v>
+        <v>-17.54570492973545</v>
       </c>
       <c r="F61">
-        <v>8.087641563242448</v>
+        <v>7.963174390767406</v>
       </c>
       <c r="G61">
-        <v>-9.868155824563397</v>
+        <v>-9.0597883660724</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.250699809632113</v>
       </c>
       <c r="E62">
-        <v>-17.11003306176094</v>
+        <v>-17.50136524563158</v>
       </c>
       <c r="F62">
-        <v>7.694556379591999</v>
+        <v>8.072470842627578</v>
       </c>
       <c r="G62">
-        <v>-9.83952901012184</v>
+        <v>-9.234595991659571</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.480945233685503</v>
       </c>
       <c r="E63">
-        <v>-15.35245217405205</v>
+        <v>-16.14724391886184</v>
       </c>
       <c r="F63">
-        <v>7.773287731023675</v>
+        <v>8.03021416467597</v>
       </c>
       <c r="G63">
-        <v>-10.52441869243154</v>
+        <v>-9.912943148023945</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.712946595190292</v>
       </c>
       <c r="E64">
-        <v>-15.23156880523159</v>
+        <v>-16.5677524122894</v>
       </c>
       <c r="F64">
-        <v>7.648649914863656</v>
+        <v>7.701852639675857</v>
       </c>
       <c r="G64">
-        <v>-9.782289740333976</v>
+        <v>-10.0451878045422</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.949064922203144</v>
       </c>
       <c r="E65">
-        <v>-15.06134113266084</v>
+        <v>-16.55450782137452</v>
       </c>
       <c r="F65">
-        <v>7.854419691188665</v>
+        <v>7.904391783129947</v>
       </c>
       <c r="G65">
-        <v>-9.528075012635798</v>
+        <v>-9.793921912859682</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.190045575345682</v>
       </c>
       <c r="E66">
-        <v>-14.96981266148427</v>
+        <v>-15.86193906690274</v>
       </c>
       <c r="F66">
-        <v>7.640444107371524</v>
+        <v>7.749291584099379</v>
       </c>
       <c r="G66">
-        <v>-9.863047902770884</v>
+        <v>-9.781144928830773</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.421735676235732</v>
       </c>
       <c r="E67">
-        <v>-14.07134430237278</v>
+        <v>-15.55133285155279</v>
       </c>
       <c r="F67">
-        <v>7.63028169607398</v>
+        <v>7.602040994577739</v>
       </c>
       <c r="G67">
-        <v>-10.64553635550247</v>
+        <v>-9.727337482807929</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.646482729727554</v>
       </c>
       <c r="E68">
-        <v>-15.29752180106986</v>
+        <v>-15.16543306809502</v>
       </c>
       <c r="F68">
-        <v>7.878170641361732</v>
+        <v>7.564665057363425</v>
       </c>
       <c r="G68">
-        <v>-10.32670178305735</v>
+        <v>-9.984276522486933</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.858377613773818</v>
       </c>
       <c r="E69">
-        <v>-14.0771671046502</v>
+        <v>-15.48295438030081</v>
       </c>
       <c r="F69">
-        <v>7.409100972587289</v>
+        <v>7.639312557499299</v>
       </c>
       <c r="G69">
-        <v>-10.36476643919578</v>
+        <v>-9.914876404393665</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.04577901587508</v>
       </c>
       <c r="E70">
-        <v>-14.60945928088552</v>
+        <v>-15.07982292305633</v>
       </c>
       <c r="F70">
-        <v>7.775905372016521</v>
+        <v>7.635102794358272</v>
       </c>
       <c r="G70">
-        <v>-10.68507738770718</v>
+        <v>-8.945856777488512</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.21259127001658</v>
       </c>
       <c r="E71">
-        <v>-14.33844562909516</v>
+        <v>-15.36990396803898</v>
       </c>
       <c r="F71">
-        <v>7.265659216383721</v>
+        <v>7.063965007680486</v>
       </c>
       <c r="G71">
-        <v>-10.42528741493468</v>
+        <v>-9.73509269961583</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.34757065900291</v>
       </c>
       <c r="E72">
-        <v>-13.7930168454394</v>
+        <v>-14.35251670906368</v>
       </c>
       <c r="F72">
-        <v>7.668065190050471</v>
+        <v>7.449470629595321</v>
       </c>
       <c r="G72">
-        <v>-10.02516339352836</v>
+        <v>-9.558105102295078</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.44391758169424</v>
       </c>
       <c r="E73">
-        <v>-13.95205991991238</v>
+        <v>-14.9526723583467</v>
       </c>
       <c r="F73">
-        <v>8.206106385516806</v>
+        <v>7.353872061107841</v>
       </c>
       <c r="G73">
-        <v>-8.957840095161721</v>
+        <v>-9.272887782577429</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.50785302769493</v>
       </c>
       <c r="E74">
-        <v>-14.39984670532142</v>
+        <v>-14.05375960562346</v>
       </c>
       <c r="F74">
-        <v>6.94630535852165</v>
+        <v>7.338802401316112</v>
       </c>
       <c r="G74">
-        <v>-9.319738899637255</v>
+        <v>-9.626633231694916</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.5279329642997</v>
       </c>
       <c r="E75">
-        <v>-14.43314300051257</v>
+        <v>-14.88936080491101</v>
       </c>
       <c r="F75">
-        <v>7.55472133506022</v>
+        <v>7.240384070189503</v>
       </c>
       <c r="G75">
-        <v>-9.794778237085568</v>
+        <v>-9.460157797470282</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.50726856640287</v>
       </c>
       <c r="E76">
-        <v>-13.20776291838986</v>
+        <v>-15.27307599921192</v>
       </c>
       <c r="F76">
-        <v>7.498442053714022</v>
+        <v>7.392362980846323</v>
       </c>
       <c r="G76">
-        <v>-9.120861514292313</v>
+        <v>-8.913205500259753</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.45002027697694</v>
       </c>
       <c r="E77">
-        <v>-15.83071107095135</v>
+        <v>-15.5341053309774</v>
       </c>
       <c r="F77">
-        <v>7.458156890181076</v>
+        <v>7.641585597652582</v>
       </c>
       <c r="G77">
-        <v>-9.36410980933552</v>
+        <v>-8.765724538307763</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.34738733020626</v>
       </c>
       <c r="E78">
-        <v>-13.98793120612493</v>
+        <v>-15.41600461374457</v>
       </c>
       <c r="F78">
-        <v>7.438642210905925</v>
+        <v>7.520920631556389</v>
       </c>
       <c r="G78">
-        <v>-9.174658517336793</v>
+        <v>-8.343963971102594</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.20561014728809</v>
       </c>
       <c r="E79">
-        <v>-15.62021386137507</v>
+        <v>-15.28780328656977</v>
       </c>
       <c r="F79">
-        <v>7.426968857465675</v>
+        <v>7.419041381420883</v>
       </c>
       <c r="G79">
-        <v>-9.175608828367958</v>
+        <v>-7.950207555754002</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.02339197634225</v>
       </c>
       <c r="E80">
-        <v>-14.92902397306313</v>
+        <v>-16.4629378180847</v>
       </c>
       <c r="F80">
-        <v>7.158637461411637</v>
+        <v>7.259439833923502</v>
       </c>
       <c r="G80">
-        <v>-7.767243964064192</v>
+        <v>-8.236161105446344</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.793399930129496</v>
       </c>
       <c r="E81">
-        <v>-15.30156702890025</v>
+        <v>-16.39909465359944</v>
       </c>
       <c r="F81">
-        <v>7.260031288249102</v>
+        <v>7.378991474230332</v>
       </c>
       <c r="G81">
-        <v>-8.182223122193944</v>
+        <v>-7.534270254359311</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.524635405004036</v>
       </c>
       <c r="E82">
-        <v>-16.23100588486098</v>
+        <v>-16.93722624495747</v>
       </c>
       <c r="F82">
-        <v>7.193246651500599</v>
+        <v>7.121206851948738</v>
       </c>
       <c r="G82">
-        <v>-6.856925623917925</v>
+        <v>-7.156847962545019</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.21310111845427</v>
       </c>
       <c r="E83">
-        <v>-16.86142598506803</v>
+        <v>-17.45412246681166</v>
       </c>
       <c r="F83">
-        <v>7.589608856596524</v>
+        <v>7.317877840721397</v>
       </c>
       <c r="G83">
-        <v>-8.478322025367353</v>
+        <v>-6.992159582993001</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.857623202475006</v>
       </c>
       <c r="E84">
-        <v>-18.81190277275858</v>
+        <v>-19.03876778816601</v>
       </c>
       <c r="F84">
-        <v>7.915263276924287</v>
+        <v>7.141374284737295</v>
       </c>
       <c r="G84">
-        <v>-6.590431259035444</v>
+        <v>-6.509848016486142</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.471836854441968</v>
       </c>
       <c r="E85">
-        <v>-18.90073165657401</v>
+        <v>-19.20639139723609</v>
       </c>
       <c r="F85">
-        <v>7.517403383564102</v>
+        <v>7.050389722683408</v>
       </c>
       <c r="G85">
-        <v>-7.82863301237963</v>
+        <v>-6.654877489267077</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.054223383757634</v>
       </c>
       <c r="E86">
-        <v>-20.15178273789549</v>
+        <v>-19.92858500808788</v>
       </c>
       <c r="F86">
-        <v>6.692680797336914</v>
+        <v>6.96216528081565</v>
       </c>
       <c r="G86">
-        <v>-7.634836136008995</v>
+        <v>-6.653921956746728</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.615867368591642</v>
       </c>
       <c r="E87">
-        <v>-21.7507732511658</v>
+        <v>-21.25162785451393</v>
       </c>
       <c r="F87">
-        <v>7.551424432797078</v>
+        <v>6.852776051806363</v>
       </c>
       <c r="G87">
-        <v>-7.485715626453786</v>
+        <v>-6.205560512902706</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.171733801873926</v>
       </c>
       <c r="E88">
-        <v>-22.70185033812889</v>
+        <v>-23.30942362283806</v>
       </c>
       <c r="F88">
-        <v>6.762326615094685</v>
+        <v>7.09639062129567</v>
       </c>
       <c r="G88">
-        <v>-6.790422126948496</v>
+        <v>-6.010360361314349</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.726382222841322</v>
       </c>
       <c r="E89">
-        <v>-23.46635686595803</v>
+        <v>-23.64620337595708</v>
       </c>
       <c r="F89">
-        <v>6.922763156934089</v>
+        <v>6.617761592692921</v>
       </c>
       <c r="G89">
-        <v>-7.327005852015418</v>
+        <v>-5.250121979360524</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.297413445390672</v>
       </c>
       <c r="E90">
-        <v>-26.87734779492646</v>
+        <v>-25.29874539604973</v>
       </c>
       <c r="F90">
-        <v>6.582390304593383</v>
+        <v>6.494205624360958</v>
       </c>
       <c r="G90">
-        <v>-6.139271096989749</v>
+        <v>-5.57361673090078</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.89481180627563</v>
       </c>
       <c r="E91">
-        <v>-27.75722222693669</v>
+        <v>-26.6463461810395</v>
       </c>
       <c r="F91">
-        <v>6.767768988931079</v>
+        <v>6.382704058474534</v>
       </c>
       <c r="G91">
-        <v>-6.729967725196676</v>
+        <v>-5.448071245003324</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.519791900631705</v>
       </c>
       <c r="E92">
-        <v>-28.69821116359176</v>
+        <v>-28.71953998035042</v>
       </c>
       <c r="F92">
-        <v>6.396040773659606</v>
+        <v>6.142764126784046</v>
       </c>
       <c r="G92">
-        <v>-6.006373754323718</v>
+        <v>-5.310542441432658</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.184082545291188</v>
       </c>
       <c r="E93">
-        <v>-32.03517110069513</v>
+        <v>-30.46710332234383</v>
       </c>
       <c r="F93">
-        <v>6.868813244724562</v>
+        <v>5.386746332945049</v>
       </c>
       <c r="G93">
-        <v>-6.28511512208311</v>
+        <v>-5.081292958887001</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.88275841588607</v>
       </c>
       <c r="E94">
-        <v>-33.8861805537617</v>
+        <v>-32.47186881186688</v>
       </c>
       <c r="F94">
-        <v>6.313379647269048</v>
+        <v>5.374383777825669</v>
       </c>
       <c r="G94">
-        <v>-6.604743360883928</v>
+        <v>-5.563291236042927</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.609738045176409</v>
       </c>
       <c r="E95">
-        <v>-35.63740495153794</v>
+        <v>-34.46110752085205</v>
       </c>
       <c r="F95">
-        <v>5.466214931365217</v>
+        <v>4.902544048456265</v>
       </c>
       <c r="G95">
-        <v>-6.753605406724616</v>
+        <v>-5.480360934106214</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.361683375196272</v>
       </c>
       <c r="E96">
-        <v>-37.59796573632518</v>
+        <v>-36.26927659910302</v>
       </c>
       <c r="F96">
-        <v>4.673873226913462</v>
+        <v>4.252340249916071</v>
       </c>
       <c r="G96">
-        <v>-6.333664528499453</v>
+        <v>-5.447541263851329</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.125288437929902</v>
       </c>
       <c r="E97">
-        <v>-39.99879807062918</v>
+        <v>-38.43460108523261</v>
       </c>
       <c r="F97">
-        <v>5.755793951301063</v>
+        <v>3.687030856284383</v>
       </c>
       <c r="G97">
-        <v>-6.520914962807871</v>
+        <v>-5.823342283274539</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.885946193768373</v>
       </c>
       <c r="E98">
-        <v>-42.26849691056304</v>
+        <v>-40.95173371966013</v>
       </c>
       <c r="F98">
-        <v>5.156851184380908</v>
+        <v>3.477496978481053</v>
       </c>
       <c r="G98">
-        <v>-6.462885942781196</v>
+        <v>-5.656513093157809</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.642813130107346</v>
       </c>
       <c r="E99">
-        <v>-44.39161438660406</v>
+        <v>-43.32569892990381</v>
       </c>
       <c r="F99">
-        <v>4.433706322554607</v>
+        <v>2.994207554870155</v>
       </c>
       <c r="G99">
-        <v>-6.102986968662456</v>
+        <v>-5.178428322143962</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.370482545660343</v>
       </c>
       <c r="E100">
-        <v>-47.32504623478142</v>
+        <v>-45.29164435317368</v>
       </c>
       <c r="F100">
-        <v>4.05221828254335</v>
+        <v>2.704491025945444</v>
       </c>
       <c r="G100">
-        <v>-6.975004380284796</v>
+        <v>-5.150947624577904</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.087275289060297</v>
       </c>
       <c r="E101">
-        <v>-48.82524742517653</v>
+        <v>-48.07316834393411</v>
       </c>
       <c r="F101">
-        <v>3.131343778403612</v>
+        <v>1.920126499582648</v>
       </c>
       <c r="G101">
-        <v>-5.877355978120082</v>
+        <v>-5.237240565547971</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.758526998156311</v>
       </c>
       <c r="E102">
-        <v>-50.71327548908413</v>
+        <v>-50.09571684604725</v>
       </c>
       <c r="F102">
-        <v>3.341616559930239</v>
+        <v>1.449835817256479</v>
       </c>
       <c r="G102">
-        <v>-5.344863289827434</v>
+        <v>-5.33587188545564</v>
       </c>
     </row>
   </sheetData>
